--- a/outputs/evaluation/architecture/validation/CF_M04/CF_M04_arch_eval_avg_by_type.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/CF_M04_arch_eval_avg_by_type.xlsx
@@ -468,22 +468,22 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8571</v>
+        <v>0.7143</v>
       </c>
     </row>
     <row r="3">
@@ -496,21 +496,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G3" t="n">
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -526,22 +524,22 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6667</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3333</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1667</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="5">
@@ -586,22 +584,22 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>4.3333</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3.3333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9167</v>
+        <v>0.8333</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="7">
@@ -614,19 +612,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>8.333299999999999</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3.3333</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5602</v>
+        <v>0.6019</v>
       </c>
       <c r="H7" t="n">
         <v>0.8333</v>
@@ -670,22 +668,22 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
+        <v>2.3333</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.3333</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
         <v>2.6667</v>
       </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
       <c r="G9" t="n">
-        <v>0.7778</v>
+        <v>0.5556</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="10">
